--- a/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0002T0006Z000C1N36_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0002T0006Z000C1N36_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>15.39912736631509</v>
+        <v>2.502358197026202</v>
       </c>
       <c r="D2" t="n">
-        <v>14.51812558058225</v>
+        <v>2.359195406844616</v>
       </c>
       <c r="E2" t="n">
-        <v>10.50378311486606</v>
+        <v>1.706864756165736</v>
       </c>
       <c r="F2" t="n">
-        <v>10.24245190388755</v>
+        <v>1.664398434381728</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>10.61971875245699</v>
+        <v>1.725704297274261</v>
       </c>
       <c r="D3" t="n">
-        <v>11.00165093616145</v>
+        <v>1.787768277126236</v>
       </c>
       <c r="E3" t="n">
-        <v>10.50378311486606</v>
+        <v>1.706864756165736</v>
       </c>
       <c r="F3" t="n">
-        <v>10.24245190388755</v>
+        <v>1.664398434381728</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.79232856299297</v>
+        <v>4.028753391486359</v>
       </c>
       <c r="D4" t="n">
-        <v>23.31407235428123</v>
+        <v>3.788536757570701</v>
       </c>
       <c r="E4" t="n">
-        <v>10.50378311486606</v>
+        <v>1.706864756165736</v>
       </c>
       <c r="F4" t="n">
-        <v>10.24245190388755</v>
+        <v>1.664398434381728</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>38.14518740692522</v>
+        <v>6.198592953625349</v>
       </c>
       <c r="D5" t="n">
-        <v>37.5441341249324</v>
+        <v>6.100921795301515</v>
       </c>
       <c r="E5" t="n">
-        <v>10.50378311486606</v>
+        <v>1.706864756165736</v>
       </c>
       <c r="F5" t="n">
-        <v>10.24245190388755</v>
+        <v>1.664398434381728</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
